--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Desktop\chip_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E56D78F-B3B2-4A6F-96CC-C7C13C143C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6101DA84-149B-436E-9B02-F6A267D37206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data.xlsx!$A$1:$C$282</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
       <x15:dataModel>
@@ -299,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4371" uniqueCount="466">
   <si>
     <t>22AD121500004000</t>
   </si>
@@ -1680,6 +1679,24 @@
   <si>
     <t>443B061600004000</t>
   </si>
+  <si>
+    <t>4F3B061600004000</t>
+  </si>
+  <si>
+    <t>F10A0A1600004000</t>
+  </si>
+  <si>
+    <t>6DAF721600004000</t>
+  </si>
+  <si>
+    <t>DD59061600004000</t>
+  </si>
+  <si>
+    <t>0FAF721600004000</t>
+  </si>
+  <si>
+    <t>4F5A061600004000</t>
+  </si>
 </sst>
 </file>
 
@@ -2254,7 +2271,17 @@
     <cellStyle name="Zvýraznenie5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Zvýraznenie6" xfId="38" builtinId="49" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2288,15 +2315,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C3841" totalsRowShown="0">
-  <autoFilter ref="A1:C3841" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C4370" totalsRowShown="0">
+  <autoFilter ref="A1:C4370" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C999">
     <sortCondition ref="A1:A999"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="4" xr3:uid="{ADF7FDBC-1C20-47ED-8A60-FCEB998DB62C}" name="Dátum zvozu" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{2105C53A-A455-4B66-A74F-6750BD5FC4B5}" name="Počet kg odpadu" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{EB4F51A0-97F0-4EA9-9681-DA79BA1DD0D6}" name="Číslo čipu" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{ADF7FDBC-1C20-47ED-8A60-FCEB998DB62C}" name="Dátum zvozu" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{2105C53A-A455-4B66-A74F-6750BD5FC4B5}" name="Počet kg odpadu" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{EB4F51A0-97F0-4EA9-9681-DA79BA1DD0D6}" name="Číslo čipu" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2619,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85308AED-E7F4-43C8-AFEE-DDE995A3E6EF}">
-  <dimension ref="A1:C3841"/>
+  <dimension ref="A1:C4370"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -44878,9 +44905,5828 @@
         <v>326</v>
       </c>
     </row>
+    <row r="3842" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3842" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3842" s="7">
+        <v>3</v>
+      </c>
+      <c r="C3842" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3843" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3843" s="7">
+        <v>9</v>
+      </c>
+      <c r="C3843" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3844" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3844" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C3844" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3845" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3845" s="7">
+        <v>17</v>
+      </c>
+      <c r="C3845" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3846" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3846" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3846" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3847" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3847" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3847" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3848" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3848" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3848" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3849" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3849" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3849" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C3849" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3850" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3850" s="7">
+        <v>41.5</v>
+      </c>
+      <c r="C3850" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3851" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3851" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3851" s="7">
+        <v>65</v>
+      </c>
+      <c r="C3851" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3852" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3852" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3852" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3853" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3853" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3853" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3853" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3854" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3854" s="7">
+        <v>17</v>
+      </c>
+      <c r="C3854" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3855" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3855" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3855" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C3855" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="3856" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3856" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3856" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C3856" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3857" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3857" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C3857" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3858" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3858" s="7">
+        <v>4</v>
+      </c>
+      <c r="C3858" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3859" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3859" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3859" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3860" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3860" s="7">
+        <v>4</v>
+      </c>
+      <c r="C3860" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3861" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3861" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3861" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3862" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3862" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3862" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3862" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3863" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3863" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3863" s="7">
+        <v>33</v>
+      </c>
+      <c r="C3863" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3864" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3864" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3864" s="7">
+        <v>32</v>
+      </c>
+      <c r="C3864" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3865" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3865" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C3865" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3866" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3866" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3866" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3867" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3867" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C3867" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3868" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3868" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3868" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3868" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3869" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3869" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3869" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3870" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3870" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3870" s="7">
+        <v>45</v>
+      </c>
+      <c r="C3870" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3871" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3871" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3871" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C3871" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3872" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3872" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C3872" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3873" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3873" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3873" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3874" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3874" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3874" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3875" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3875" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3875" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3875" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3876" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3876" s="7">
+        <v>3</v>
+      </c>
+      <c r="C3876" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3877" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3877" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3877" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3877" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3878" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3878" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3878" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3878" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3879" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3879" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C3879" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3880" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3880" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3880" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3881" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3881" s="7">
+        <v>11</v>
+      </c>
+      <c r="C3881" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3882" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3882" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3882" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3882" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3883" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3883" s="7">
+        <v>11</v>
+      </c>
+      <c r="C3883" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="3884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3884" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3884" s="7">
+        <v>40</v>
+      </c>
+      <c r="C3884" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3885" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C3885" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3886" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3886" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3886" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3887" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3887" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3887" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3887" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3888" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3888" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3888" s="7">
+        <v>20</v>
+      </c>
+      <c r="C3888" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3889" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3889" s="7">
+        <v>32</v>
+      </c>
+      <c r="C3889" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3890" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3890" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3890" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3891" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3891" s="7">
+        <v>18</v>
+      </c>
+      <c r="C3891" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3892" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3892" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3892" s="7">
+        <v>14</v>
+      </c>
+      <c r="C3892" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3893" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3893" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C3893" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3894" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3894" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3894" s="7">
+        <v>11</v>
+      </c>
+      <c r="C3894" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="3895" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3895" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3895" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3895" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3896" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3896" s="7">
+        <v>7</v>
+      </c>
+      <c r="C3896" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3897" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3897" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3897" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3898" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3898" s="7">
+        <v>14</v>
+      </c>
+      <c r="C3898" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3899" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3899" s="7">
+        <v>10</v>
+      </c>
+      <c r="C3899" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3900" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3900" s="7">
+        <v>40</v>
+      </c>
+      <c r="C3900" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3901" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3901" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C3901" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3902" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3902" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C3902" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3903" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3903" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C3903" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3904" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3904" s="7">
+        <v>15</v>
+      </c>
+      <c r="C3904" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3905" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3905" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3905" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3906" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3906" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3906" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3906" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3907" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3907" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C3907" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3908" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3908" s="7">
+        <v>3</v>
+      </c>
+      <c r="C3908" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="3909" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3909" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3909" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C3909" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3910" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3910" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3910" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3910" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3911" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3911" s="7">
+        <v>7</v>
+      </c>
+      <c r="C3911" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3912" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3912" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3912" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3912" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3913" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3913" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3913" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C3913" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3914" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3914" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3914" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C3914" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3915" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3915" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3915" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C3915" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3916" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3916" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3916" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3916" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3917" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3917" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3917" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3917" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3918" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3918" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3918" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C3918" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3919" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3919" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3919" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C3919" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3920" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3920" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3920" s="7">
+        <v>14</v>
+      </c>
+      <c r="C3920" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3921" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3921" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3921" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C3921" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3922" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3922" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3922" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3922" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3923" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3923" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3923" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3923" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3924" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3924" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3924" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3924" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3925" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3925" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3925" s="7">
+        <v>23</v>
+      </c>
+      <c r="C3925" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3926" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3926" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3926" s="7">
+        <v>36</v>
+      </c>
+      <c r="C3926" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3927" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3927" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3927" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3927" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3928" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3928" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3928" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3928" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3929" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3929" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3929" s="7">
+        <v>3</v>
+      </c>
+      <c r="C3929" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3930" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3930" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3930" s="7">
+        <v>12</v>
+      </c>
+      <c r="C3930" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3931" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3931" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3931" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C3931" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3932" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3932" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3932" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C3932" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3933" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3933" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3933" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3933" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3934" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3934" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3934" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3934" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3935" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3935" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3935" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C3935" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="3936" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3936" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3936" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C3936" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3937" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3937" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3937" s="7">
+        <v>15</v>
+      </c>
+      <c r="C3937" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3938" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3938" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3938" s="7">
+        <v>6</v>
+      </c>
+      <c r="C3938" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3939" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3939" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3939" s="7">
+        <v>22</v>
+      </c>
+      <c r="C3939" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3940" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3940" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3940" s="7">
+        <v>9</v>
+      </c>
+      <c r="C3940" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="3941" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3941" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3941" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3941" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3942" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3942" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3942" s="7">
+        <v>18</v>
+      </c>
+      <c r="C3942" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3943" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3943" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C3943" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3944" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3944" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C3944" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3945" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3945" s="7">
+        <v>9</v>
+      </c>
+      <c r="C3945" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3946" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3946" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C3946" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3947" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3947" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3947" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3948" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3948" s="7">
+        <v>23</v>
+      </c>
+      <c r="C3948" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3949" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3949" s="7">
+        <v>8</v>
+      </c>
+      <c r="C3949" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3950" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3950" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3950" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3951" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3951" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3951" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3951" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3952" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3952" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C3952" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3953" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3953" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C3953" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3954" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3954" s="7">
+        <v>12</v>
+      </c>
+      <c r="C3954" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3955" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3955" s="7">
+        <v>27</v>
+      </c>
+      <c r="C3955" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3956" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3956" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C3956" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3957" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3957" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C3957" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3958" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3958" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C3958" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3959" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3959" s="7">
+        <v>15</v>
+      </c>
+      <c r="C3959" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3960" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3960" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3960" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3961" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3961" s="7">
+        <v>28</v>
+      </c>
+      <c r="C3961" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3962" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3962" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C3962" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3963" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3963" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3963" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3964" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3964" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C3964" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3965" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3965" s="7">
+        <v>20</v>
+      </c>
+      <c r="C3965" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3966" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3966" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C3966" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3967" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3967" s="7">
+        <v>5</v>
+      </c>
+      <c r="C3967" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3968" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3968" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3968" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3969" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3969" s="7">
+        <v>10</v>
+      </c>
+      <c r="C3969" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3970" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3970" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C3970" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3971" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3971" s="7">
+        <v>16</v>
+      </c>
+      <c r="C3971" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3972" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3972" s="7">
+        <v>14</v>
+      </c>
+      <c r="C3972" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3973" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3973" s="7">
+        <v>19</v>
+      </c>
+      <c r="C3973" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3974" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3974" s="7">
+        <v>27</v>
+      </c>
+      <c r="C3974" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3975" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3975" s="7">
+        <v>9</v>
+      </c>
+      <c r="C3975" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3976" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3976" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C3976" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="3977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3977" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3977" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C3977" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3978" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3978" s="7">
+        <v>21</v>
+      </c>
+      <c r="C3978" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3979" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3979" s="7">
+        <v>40</v>
+      </c>
+      <c r="C3979" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3980" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3980" s="7">
+        <v>50</v>
+      </c>
+      <c r="C3980" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3981" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3981" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="C3981" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3982" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3982" s="7">
+        <v>6</v>
+      </c>
+      <c r="C3982" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3983" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3983" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C3983" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3984" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3984" s="7">
+        <v>100</v>
+      </c>
+      <c r="C3984" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3985" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3985" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C3985" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3986" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3986" s="7">
+        <v>72</v>
+      </c>
+      <c r="C3986" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3987" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3987" s="7">
+        <v>90</v>
+      </c>
+      <c r="C3987" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3988" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3988" s="7">
+        <v>105</v>
+      </c>
+      <c r="C3988" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3989" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3989" s="7">
+        <v>115</v>
+      </c>
+      <c r="C3989" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3990" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3990" s="7">
+        <v>43.5</v>
+      </c>
+      <c r="C3990" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3991" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3991" s="7">
+        <v>42.5</v>
+      </c>
+      <c r="C3991" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3992" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3992" s="7">
+        <v>38</v>
+      </c>
+      <c r="C3992" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3993" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3993" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3993" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3994" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3994" s="7">
+        <v>21</v>
+      </c>
+      <c r="C3994" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3995" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3995" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C3995" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3996" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3996" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3996" s="7">
+        <v>11</v>
+      </c>
+      <c r="C3996" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3997" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3997" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C3997" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3998" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3998" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C3998" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3999" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B3999" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3999" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4000" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4000" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4000" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4000" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4001" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4001" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4001" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4002" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4002" s="7">
+        <v>36</v>
+      </c>
+      <c r="C4002" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4003" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4003" s="7">
+        <v>28</v>
+      </c>
+      <c r="C4003" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4004" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4004" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4004" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4005" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4005" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4005" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4006" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4006" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4006" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4007" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4007" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4007" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4008" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4008" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4008" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4009" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4009" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4009" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4010" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4010" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4010" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4011" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4011" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4011" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4012" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4012" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4012" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4012" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4013" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4013" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4013" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4013" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4014" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4014" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4014" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4015" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4015" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4015" s="7">
+        <v>29</v>
+      </c>
+      <c r="C4015" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4016" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4016" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4016" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4017" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4017" s="7">
+        <v>60</v>
+      </c>
+      <c r="C4017" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4018" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4018" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4018" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4019" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4019" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4019" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4020" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4020" s="7">
+        <v>90</v>
+      </c>
+      <c r="C4020" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4021" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4021" s="7">
+        <v>135</v>
+      </c>
+      <c r="C4021" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4022" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4022" s="7">
+        <v>95</v>
+      </c>
+      <c r="C4022" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4023" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4023" s="7">
+        <v>35</v>
+      </c>
+      <c r="C4023" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4024" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4024" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4024" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4025" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4025" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4025" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4026" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4026" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C4026" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4027" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4027" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4027" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4027" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4028" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4028" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4028" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4028" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4029" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4029" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4029" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4029" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4030" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4030" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4030" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4030" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4031" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4031" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4031" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4031" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4032" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4032" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4032" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4033" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4033" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4033" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4033" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4034" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4034" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4034" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4034" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4035" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4035" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4035" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4035" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4036" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4036" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4036" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4036" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4037" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4037" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4037" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4037" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4038" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4038" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4038" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4039" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4039" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4039" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4039" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4040" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4040" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4040" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4040" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4041" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4041" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4041" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4042" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4042" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4042" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4043" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4043" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4043" s="7">
+        <v>26</v>
+      </c>
+      <c r="C4043" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4044" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4044" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4044" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4044" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4045" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4045" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4045" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4045" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4046" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4046" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4046" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4046" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4047" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4047" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4047" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4047" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4048" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4048" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4048" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4048" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4049" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4049" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4049" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4049" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4050" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4050" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4050" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4050" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4051" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4051" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4051" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4051" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4052" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4052" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4052" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4052" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4053" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4053" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4053" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4053" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4054" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4054" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4054" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4054" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4055" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4055" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4055" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4055" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4056" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4056" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4056" s="7">
+        <v>32</v>
+      </c>
+      <c r="C4056" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4057" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4057" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4057" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4057" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4058" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4058" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4058" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4058" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4059" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4059" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4059" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4059" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4060" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4060" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4060" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4061" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4061" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4061" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4062" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4062" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4062" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4063" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4063" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4063" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4064" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4064" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4064" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4065" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4065" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4065" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4066" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4066" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4066" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4067" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4067" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4067" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4068" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4068" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4068" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4069" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4069" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4069" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4070" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4070" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C4070" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4071" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4071" s="7">
+        <v>42.5</v>
+      </c>
+      <c r="C4071" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4072" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4072" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4072" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4073" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4073" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4073" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4074" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4074" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4074" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4075" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4075" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4075" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4076" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4076" s="7">
+        <v>30</v>
+      </c>
+      <c r="C4076" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4077" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4077" s="7">
+        <v>50</v>
+      </c>
+      <c r="C4077" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4078" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4078" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4078" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4079" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4079" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4079" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4080" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4080" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4080" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4081" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4081" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4081" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4082" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4082" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C4082" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4083" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4083" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4083" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4084" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4084" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4084" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4085" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4085" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4085" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4086" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4086" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4086" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4087" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4087" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4087" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4088" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4088" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4088" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4089" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4089" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4089" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4090" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4090" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4090" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4091" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4091" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4091" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4092" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4092" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4092" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4093" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4093" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4093" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4094" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4094" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4094" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4095" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4095" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4095" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4096" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4096" s="7">
+        <v>32</v>
+      </c>
+      <c r="C4096" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4097" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4097" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4097" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4098" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4098" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4098" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4099" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4099" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4099" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4100" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4100" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4100" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4101" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4101" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4101" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4102" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B4102" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4102" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4103" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4103" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4103" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4104" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4104" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4104" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4105" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4105" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4105" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4106" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4106" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4106" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4107" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4107" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4107" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4108" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4108" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4108" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4109" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4109" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4109" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4110" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4110" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4110" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4111" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4111" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4111" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4112" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4112" s="7">
+        <v>53</v>
+      </c>
+      <c r="C4112" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4113" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4113" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4113" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4114" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4114" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4114" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4115" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4115" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4115" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4116" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4116" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4116" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4117" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4117" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4117" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4118" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4118" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4118" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4119" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4119" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C4119" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4120" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4120" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4120" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4121" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4121" s="7">
+        <v>73</v>
+      </c>
+      <c r="C4121" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4122" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4122" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C4122" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4123" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4123" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4123" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4124" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4124" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4124" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4125" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4125" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4125" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4126" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4126" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4126" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4127" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4127" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4127" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4128" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4128" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4128" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4129" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4129" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4129" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4130" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4130" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4130" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4131" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4131" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4131" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4132" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4132" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4132" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4133" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4133" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4133" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4134" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4134" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4134" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4135" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4135" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4135" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4136" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4136" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4136" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4137" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4137" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4137" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4138" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4138" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4138" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4139" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4139" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4139" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4140" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4140" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4140" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4141" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4141" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C4141" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4142" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4142" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4142" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4143" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4143" s="7">
+        <v>32</v>
+      </c>
+      <c r="C4143" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4144" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4144" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4144" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4145" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4145" s="7">
+        <v>46.5</v>
+      </c>
+      <c r="C4145" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4146" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4146" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4146" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4147" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4147" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4147" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4148" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4148" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4148" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4149" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4149" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4149" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4150" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4150" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4150" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4151" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4151" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C4151" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4152" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4152" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4152" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4153" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4153" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4153" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4154" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4154" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C4154" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4155" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4155" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C4155" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4156" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4156" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C4156" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4157" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4157" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4157" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4158" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4158" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4158" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4159" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4159" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4159" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4160" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4160" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4160" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4161" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4161" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4161" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4162" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4162" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4162" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4163" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4163" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4163" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4164" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4164" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4164" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4165" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4165" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4165" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4166" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4166" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4166" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4167" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4167" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4167" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4168" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4168" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C4168" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4169" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4169" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4169" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4170" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4170" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4170" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4171" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4171" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4171" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4172" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4172" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4172" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4173" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4173" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C4173" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4174" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4174" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4174" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4175" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4175" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4175" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4176" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4176" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4176" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4177" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4177" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4177" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4178" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4178" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4178" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4179" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4179" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4179" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4180" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4180" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4180" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4181" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4181" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4181" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4182" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4182" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4182" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4183" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4183" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4183" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4184" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4184" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4184" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4185" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4185" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4185" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4186" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4186" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C4186" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4187" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4187" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4187" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4188" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4188" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4188" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4189" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4189" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4189" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4190" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4190" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4190" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4191" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4191" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4191" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4192" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4192" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4192" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4193" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4193" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4193" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4194" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4194" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4194" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4195" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4195" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4195" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4196" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4196" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4196" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4197" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4197" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4197" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4198" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4198" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4198" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4199" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4199" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4199" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4200" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4200" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4200" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4201" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4201" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4201" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4202" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4202" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4202" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4203" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4203" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4203" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4204" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4204" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4204" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4205" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4205" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4205" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4206" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4206" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4206" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4207" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4207" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4207" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4208" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4208" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4208" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4209" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4209" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4209" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4210" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4210" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4210" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4211" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4211" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4211" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4212" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4212" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4212" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4213" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4213" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4213" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4214" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4214" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4214" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4215" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4215" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4215" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4216" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4216" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4216" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4217" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4217" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4217" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4218" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4218" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4218" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4219" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4219" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4219" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4220" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4220" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4220" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4221" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4221" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4221" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4222" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4222" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4222" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4223" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4223" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4223" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4224" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4224" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4224" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4225" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4225" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4225" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4226" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4226" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4226" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4227" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4227" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4227" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4228" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4228" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4228" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4229" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4229" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4229" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4230" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4230" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4230" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4231" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4231" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4231" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4232" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4232" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4232" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4233" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4233" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4233" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4234" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4234" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C4234" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4235" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4235" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4235" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4236" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4236" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4236" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4237" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4237" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4237" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4238" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4238" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4238" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4239" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4239" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4239" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4240" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4240" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4240" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4241" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4241" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4241" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4242" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4242" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4242" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4243" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4243" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4243" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4244" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4244" s="7">
+        <v>110</v>
+      </c>
+      <c r="C4244" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4245" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4245" s="7">
+        <v>95</v>
+      </c>
+      <c r="C4245" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4246" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4246" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4246" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4247" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4247" s="7">
+        <v>85</v>
+      </c>
+      <c r="C4247" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4248" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4248" s="7">
+        <v>145</v>
+      </c>
+      <c r="C4248" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4249" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4249" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="C4249" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4250" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4250" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4250" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4251" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4251" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4251" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4252" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4252" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4252" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4253" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4253" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4253" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4254" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4254" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4254" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4255" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4255" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4255" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4256" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4256" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4256" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4257" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4257" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4257" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4258" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4258" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4258" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4259" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4259" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4259" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4260" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4260" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4260" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4261" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4261" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4261" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4262" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4262" s="7">
+        <v>26</v>
+      </c>
+      <c r="C4262" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4263" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4263" s="7">
+        <v>33</v>
+      </c>
+      <c r="C4263" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4264" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4264" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C4264" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4265" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4265" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4265" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4266" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4266" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4266" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4267" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4267" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4267" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4268" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4268" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4268" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4269" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4269" s="7">
+        <v>60</v>
+      </c>
+      <c r="C4269" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4270" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4270" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C4270" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4271" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4271" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4271" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4272" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4272" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4272" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4273" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4273" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4273" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4274" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4274" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4274" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4275" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4275" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4275" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4276" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4276" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C4276" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4277" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4277" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4277" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4278" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4278" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4278" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4279" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4279" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4279" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4280" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4280" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4280" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4281" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4281" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4281" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4282" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4282" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4282" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4283" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4283" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4283" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4284" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4284" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4284" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4285" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4285" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4285" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4286" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4286" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4286" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4287" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4287" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4287" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4288" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4288" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4288" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4289" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4289" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C4289" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4290" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4290" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4290" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4291" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4291" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4291" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4292" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4292" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4292" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4293" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4293" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4293" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4294" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4294" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4294" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4295" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4295" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4295" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4296" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4296" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4296" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4297" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4297" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4297" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4298" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4298" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4298" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4299" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4299" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4299" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4300" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4300" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4300" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4301" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4301" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4301" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4302" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4302" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4302" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4303" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4303" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4303" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4304" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4304" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4304" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4305" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4305" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4305" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4306" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4306" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4306" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4307" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4307" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4307" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4308" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4308" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4308" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4309" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4309" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4309" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4310" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4310" s="7">
+        <v>30</v>
+      </c>
+      <c r="C4310" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4311" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4311" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4311" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4312" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4312" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4312" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4313" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4313" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4313" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4314" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4314" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4314" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4315" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4315" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4315" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4316" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4316" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4316" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4317" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4317" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4317" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4318" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4318" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C4318" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4319" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4319" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4319" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4320" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4320" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4320" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4321" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4321" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4321" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4322" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4322" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4322" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4323" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4323" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4323" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4324" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4324" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4324" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4325" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4325" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4325" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4326" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4326" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4326" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4327" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4327" s="7">
+        <v>55</v>
+      </c>
+      <c r="C4327" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4328" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4328" s="7">
+        <v>80</v>
+      </c>
+      <c r="C4328" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4329" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4329" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4329" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4330" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4330" s="7">
+        <v>28</v>
+      </c>
+      <c r="C4330" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4331" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4331" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4331" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4332" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4332" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C4332" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4333" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4333" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4333" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4334" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4334" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4334" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4335" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4335" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4335" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4336" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4336" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4336" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4337" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4337" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4337" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4338" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4338" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4338" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4339" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4339" s="7">
+        <v>27</v>
+      </c>
+      <c r="C4339" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4340" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4340" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4340" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4341" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4341" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4341" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4342" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4342" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4342" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4343" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4343" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4343" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4344" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4344" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4344" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4345" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4345" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4345" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4346" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4346" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4346" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4347" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4347" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4347" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4348" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4348" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4348" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4349" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4349" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4349" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4350" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4350" s="7">
+        <v>85</v>
+      </c>
+      <c r="C4350" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4351" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4351" s="7">
+        <v>85</v>
+      </c>
+      <c r="C4351" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4352" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4352" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4352" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4353" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4353" s="7">
+        <v>145</v>
+      </c>
+      <c r="C4353" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4354" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4354" s="7">
+        <v>105</v>
+      </c>
+      <c r="C4354" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4355" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4355" s="7">
+        <v>60</v>
+      </c>
+      <c r="C4355" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4356" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4356" s="7">
+        <v>40</v>
+      </c>
+      <c r="C4356" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4357" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4357" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4357" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4358" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4358" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4358" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4359" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4359" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4359" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4360" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4360" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4360" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4361" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4361" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4361" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4362" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4362" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4362" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4363" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4363" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4363" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4364" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4364" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4364" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4365" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4365" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4365" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4366" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4366" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4366" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4367" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4367" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4367" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4368" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4368" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4368" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4369" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4369" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4369" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4370" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B4370" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4370" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C3841">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="C2:C4370">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Desktop\chip_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanaKralikova\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6101DA84-149B-436E-9B02-F6A267D37206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE52D29F-632A-44B1-8AAD-A4497EC2A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4371" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5167" uniqueCount="467">
   <si>
     <t>22AD121500004000</t>
   </si>
@@ -1697,6 +1697,9 @@
   <si>
     <t>4F5A061600004000</t>
   </si>
+  <si>
+    <t>EE090A1600004000</t>
+  </si>
 </sst>
 </file>
 
@@ -2228,48 +2231,48 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20 % - zvýraznenie1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - zvýraznenie2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - zvýraznenie3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - zvýraznenie4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - zvýraznenie5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - zvýraznenie6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - zvýraznenie6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - zvýraznenie6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Dobrá" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Kontrolná bunka" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Nadpis 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Nadpis 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Nadpis 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Nadpis 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Názov" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Neutrálna" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
-    <cellStyle name="Poznámka" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Prepojená bunka" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Spolu" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Text upozornenia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Vstup" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Výpočet" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Výstup" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Vysvetľujúci text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Zlá" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Zvýraznenie6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -2299,7 +2302,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+      <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2315,8 +2318,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C4370" totalsRowShown="0">
-  <autoFilter ref="A1:C4370" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C5166" totalsRowShown="0">
+  <autoFilter ref="A1:C5166" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C999">
     <sortCondition ref="A1:A999"/>
   </sortState>
@@ -2330,7 +2333,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motív Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2646,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85308AED-E7F4-43C8-AFEE-DDE995A3E6EF}">
-  <dimension ref="A1:C4370"/>
+  <dimension ref="A1:C5166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -50724,8 +50727,8764 @@
         <v>273</v>
       </c>
     </row>
+    <row r="4371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4371" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4371" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4371" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4372" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4372" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4372" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4373" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4373" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C4373" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4374" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4374" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4374" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4375" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4375" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4375" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4376" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4376" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4376" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4377" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4377" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4377" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4378" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4378" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4378" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4379" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4379" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4379" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4380" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4380" s="7">
+        <v>48.5</v>
+      </c>
+      <c r="C4380" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4381" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4381" s="7">
+        <v>57</v>
+      </c>
+      <c r="C4381" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4382" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4382" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4382" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4383" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4383" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4383" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4384" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4384" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4384" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4385" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4385" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4385" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4386" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4386" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4386" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4387" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4387" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4387" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4388" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4388" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4388" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4389" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4389" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4389" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4390" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4390" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4390" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4391" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4391" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4391" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4392" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4392" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4392" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="4393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4393" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4393" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4393" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4394" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4394" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4394" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4395" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4395" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4395" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4396" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4396" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4396" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4397" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4397" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C4397" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4398" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4398" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4398" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4399" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4399" s="7">
+        <v>26</v>
+      </c>
+      <c r="C4399" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4400" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4400" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4400" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4401" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4401" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4401" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4402" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4402" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4402" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4403" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4403" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4403" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4404" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4404" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4404" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4405" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4405" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4405" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4406" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4406" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4406" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4407" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4407" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4407" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4408" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4408" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4408" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4409" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4409" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4409" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4410" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4410" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4410" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4411" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4411" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4411" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4412" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4412" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="C4412" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4413" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4413" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4413" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4414" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4414" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4414" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4415" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4415" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4415" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4416" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4416" s="7">
+        <v>29</v>
+      </c>
+      <c r="C4416" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4417" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4417" s="7">
+        <v>39</v>
+      </c>
+      <c r="C4417" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4418" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4418" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C4418" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4419" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4419" s="7">
+        <v>35</v>
+      </c>
+      <c r="C4419" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4420" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4420" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C4420" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4421" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4421" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4421" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4422" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4422" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4422" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4423" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4423" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4423" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4424" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4424" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4424" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4425" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4425" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4425" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4426" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4426" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4426" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4427" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4427" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4427" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4428" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4428" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4428" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4429" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4429" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4429" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4430" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4430" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4430" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4431" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4431" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4431" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4432" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4432" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4432" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4433" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4433" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4433" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4434" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4434" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4434" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4435" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4435" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4435" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4436" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4436" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4436" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4437" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4437" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4437" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4438" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4438" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4438" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4439" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4439" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4439" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4440" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4440" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4440" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4441" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4441" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4441" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4442" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4442" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4442" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4443" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4443" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4443" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4444" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4444" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4444" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4445" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4445" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4445" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4446" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4446" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4446" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4447" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4447" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4447" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4448" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4448" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4448" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4449" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4449" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4449" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4450" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4450" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4450" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4451" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4451" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C4451" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4452" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4452" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4452" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4453" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4453" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4453" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4454" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4454" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4454" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4455" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4455" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4455" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4456" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4456" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4456" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4457" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4457" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4457" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4458" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4458" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4458" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4459" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4459" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4459" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4460" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4460" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4460" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4461" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4461" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4461" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4462" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4462" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4462" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4463" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4463" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4463" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4464" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4464" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4464" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4465" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4465" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4465" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4466" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4466" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C4466" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4467" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4467" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4467" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4468" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4468" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4468" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4469" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4469" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4469" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4470" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4470" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4470" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4471" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4471" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4471" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4472" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4472" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4472" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4473" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4473" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4473" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4474" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4474" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4474" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4475" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4475" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4475" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4476" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4476" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4476" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4477" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4477" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4477" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4478" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4478" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4478" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4479" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4479" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4479" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4480" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4480" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4480" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4481" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4481" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4481" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4482" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4482" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4482" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4483" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4483" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4483" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4484" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4484" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4484" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4485" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4485" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4485" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4486" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4486" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4486" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4487" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4487" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4487" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4488" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4488" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C4488" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4489" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4489" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4489" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4490" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4490" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4490" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4491" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4491" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C4491" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4492" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4492" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4492" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4493" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4493" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4493" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4494" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4494" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4494" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4495" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4495" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4495" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4496" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4496" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4496" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4497" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4497" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4497" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4498" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4498" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4498" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4499" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4499" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4499" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4500" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4500" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4500" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4501" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4501" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4501" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4502" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4502" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4502" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4503" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4503" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4503" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4504" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4504" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4504" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4505" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4505" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4505" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4506" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4506" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4506" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4507" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4507" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4507" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4508" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4508" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4508" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4509" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4509" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4509" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4510" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4510" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4510" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4511" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4511" s="7">
+        <v>40</v>
+      </c>
+      <c r="C4511" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4512" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4512" s="7">
+        <v>45</v>
+      </c>
+      <c r="C4512" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4513" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4513" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4513" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4514" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4514" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4514" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4515" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4515" s="7">
+        <v>90</v>
+      </c>
+      <c r="C4515" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4516" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4516" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4516" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4517" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4517" s="7">
+        <v>120</v>
+      </c>
+      <c r="C4517" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4518" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4518" s="7">
+        <v>160</v>
+      </c>
+      <c r="C4518" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4519" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4519" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C4519" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4520" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4520" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4520" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4521" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4521" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4521" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4522" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4522" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4522" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4523" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4523" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4523" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4524" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4524" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4524" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4525" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4525" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4525" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4526" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4526" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4526" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4527" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4527" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4527" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4528" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4528" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4528" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4529" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4529" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4529" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4530" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4530" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4530" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4531" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4531" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C4531" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4532" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4532" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4532" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4533" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4533" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4533" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4534" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4534" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4534" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4535" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4535" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4535" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4536" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4536" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C4536" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4537" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4537" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4537" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4538" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4538" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4538" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4539" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4539" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4539" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4540" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4540" s="7">
+        <v>40</v>
+      </c>
+      <c r="C4540" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4541" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4541" s="7">
+        <v>40</v>
+      </c>
+      <c r="C4541" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4542" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4542" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4542" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4543" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4543" s="7">
+        <v>55</v>
+      </c>
+      <c r="C4543" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4544" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4544" s="7">
+        <v>105</v>
+      </c>
+      <c r="C4544" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4545" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4545" s="7">
+        <v>105</v>
+      </c>
+      <c r="C4545" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4546" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4546" s="7">
+        <v>55</v>
+      </c>
+      <c r="C4546" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4547" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4547" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4547" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4548" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4548" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4548" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4549" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4549" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4549" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4550" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4550" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4550" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4551" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4551" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4551" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4552" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4552" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4552" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4553" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4553" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4553" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4554" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4554" s="7">
+        <v>107</v>
+      </c>
+      <c r="C4554" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4555" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4555" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4555" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4556" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4556" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4556" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4557" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4557" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4557" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4558" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4558" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4558" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4559" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4559" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4559" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4560" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4560" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4560" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4561" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4561" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4561" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4562" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4562" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4562" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4563" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4563" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4563" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4564" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4564" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4564" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4565" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4565" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4565" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4566" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4566" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4566" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4567" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4567" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4567" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4568" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4568" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4568" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4569" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4569" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4569" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4570" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4570" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4570" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4571" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4571" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4571" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4572" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4572" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4572" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4573" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4573" s="7">
+        <v>37</v>
+      </c>
+      <c r="C4573" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4574" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4574" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4574" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4575" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4575" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4575" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4576" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4576" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4576" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4577" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4577" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4577" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4578" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4578" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4578" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4579" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4579" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4579" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4580" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4580" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4580" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4581" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4581" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4581" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4582" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4582" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4582" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4583" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4583" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4583" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4584" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4584" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4584" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4585" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4585" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4585" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4586" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4586" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4586" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4587" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4587" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4587" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4588" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4588" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4588" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4589" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4589" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4589" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4590" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4590" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4590" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4591" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4591" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4591" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4592" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4592" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4592" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4593" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4593" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4593" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4594" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4594" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4594" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4595" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4595" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4595" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4596" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4596" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4596" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4597" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4597" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4597" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4598" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4598" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4598" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4599" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4599" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4599" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4600" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4600" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4600" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4601" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4601" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4601" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4602" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4602" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4602" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4603" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4603" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4603" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4604" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4604" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4604" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4605" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4605" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4605" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4606" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4606" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4606" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4607" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4607" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4607" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4608" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4608" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4608" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4609" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4609" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4609" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4610" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4610" s="7">
+        <v>30</v>
+      </c>
+      <c r="C4610" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4611" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4611" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4611" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4612" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4612" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4612" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4613" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4613" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4613" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4614" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4614" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4614" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4615" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4615" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4615" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4616" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4616" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4616" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4617" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4617" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4617" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4618" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4618" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4618" s="7">
+        <v>90</v>
+      </c>
+      <c r="C4618" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4619" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4619" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4619" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4620" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4620" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4620" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4620" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4621" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4621" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4621" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4622" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4622" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4622" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4622" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4623" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4623" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4623" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4624" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4624" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4624" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4625" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4625" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4625" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4626" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4626" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4626" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4627" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4627" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4627" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4628" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4628" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4628" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4629" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4629" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4629" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4630" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4630" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4630" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4631" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4631" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4631" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4632" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4632" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4632" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4633" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4633" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4633" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4634" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4634" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4634" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4635" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4635" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4635" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4636" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4636" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4636" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4637" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4637" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4637" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4638" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4638" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4638" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4639" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4639" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4639" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4639" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4640" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4640" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4640" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4641" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4641" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4641" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C4641" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4642" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4642" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4642" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4643" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4643" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4643" s="7">
+        <v>39</v>
+      </c>
+      <c r="C4643" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4644" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4644" s="7">
+        <v>56</v>
+      </c>
+      <c r="C4644" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4645" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4645" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4645" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4645" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4646" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4646" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4646" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4647" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4647" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4647" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4647" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4648" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4648" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4648" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4648" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4649" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4649" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4649" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4649" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4650" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4650" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4650" s="7">
+        <v>35.5</v>
+      </c>
+      <c r="C4650" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4651" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4651" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4651" s="7">
+        <v>36</v>
+      </c>
+      <c r="C4651" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4652" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4652" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4652" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4652" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4653" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4653" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4653" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4653" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4654" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4654" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4654" s="7">
+        <v>41</v>
+      </c>
+      <c r="C4654" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4655" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4655" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4655" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4655" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4656" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4656" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4656" s="7">
+        <v>76</v>
+      </c>
+      <c r="C4656" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4657" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4657" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4657" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4657" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4658" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4658" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4658" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4658" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4659" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4659" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4659" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4660" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4660" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4660" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4660" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4661" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4661" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4661" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4661" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4662" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4662" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="C4662" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4663" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4663" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4663" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4664" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4664" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4664" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4665" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4665" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4665" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4666" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4666" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4666" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4667" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4667" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4667" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4668" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4668" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4668" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4669" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4669" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4669" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4670" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4670" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4670" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="4671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4671" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4671" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4671" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4672" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4672" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4672" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4673" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4673" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4673" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4674" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4674" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4674" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4675" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4675" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4675" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4676" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4676" s="7">
+        <v>49</v>
+      </c>
+      <c r="C4676" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4677" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4677" s="7">
+        <v>27</v>
+      </c>
+      <c r="C4677" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4678" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4678" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4678" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4679" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4679" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4679" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4680" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4680" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4680" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4681" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4681" s="7">
+        <v>60</v>
+      </c>
+      <c r="C4681" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4682" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4682" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4682" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4683" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4683" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4683" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4684" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4684" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C4684" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4685" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4685" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4685" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4686" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4686" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4686" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4687" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4687" s="7">
+        <v>29</v>
+      </c>
+      <c r="C4687" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4688" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4688" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4688" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4689" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4689" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4689" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4690" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4690" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4690" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4691" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4691" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="C4691" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4692" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4692" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4692" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4692" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4693" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4693" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4693" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4693" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4694" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4694" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4694" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4695" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4695" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4695" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4696" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4696" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4696" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4697" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4697" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4697" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4697" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4698" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4698" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4698" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4699" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4699" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4699" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4700" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4700" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4700" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4701" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4701" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4701" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4702" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4702" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4702" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4702" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4703" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4703" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4703" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4703" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4704" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4704" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4704" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4704" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4705" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4705" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4705" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4706" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4706" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4706" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4707" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4707" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4707" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4708" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4708" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4708" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4709" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4709" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4709" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4710" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4710" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4710" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4711" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4711" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4711" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4712" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4712" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4712" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4713" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4713" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4713" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4714" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4714" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C4714" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4715" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4715" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4715" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4716" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4716" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4716" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4717" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4717" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4717" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4718" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4718" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4718" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4719" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4719" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4719" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4720" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4720" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4720" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4721" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4721" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4721" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4722" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4722" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4722" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4723" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4723" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4723" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4724" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4724" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4724" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4725" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4725" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4725" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4726" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4726" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4726" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4727" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4727" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4727" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4728" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4728" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4728" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4729" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4729" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4729" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4730" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4730" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4730" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4731" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4731" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4731" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4732" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4732" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4732" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4733" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4733" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4733" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4734" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4734" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4734" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4735" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4735" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4735" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4735" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4736" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4736" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4736" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4736" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4737" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4737" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4737" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4737" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4738" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4738" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4738" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4739" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4739" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4739" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4739" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4740" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4740" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4740" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4740" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4741" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4741" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4741" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4742" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4742" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4742" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4743" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4743" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4743" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4744" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4744" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4744" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4744" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4745" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4745" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4745" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4745" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4746" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4746" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4746" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4747" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4747" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4747" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4747" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4748" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4748" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4748" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4748" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4749" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4749" s="7">
+        <v>40.5</v>
+      </c>
+      <c r="C4749" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4750" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4750" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4750" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4751" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4751" s="7">
+        <v>45</v>
+      </c>
+      <c r="C4751" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4752" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4752" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4752" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4752" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4753" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4753" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4753" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4754" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4754" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4754" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4755" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4755" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4755" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4756" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4756" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4756" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4757" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4757" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4757" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4757" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4758" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4758" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4758" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4758" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4759" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4759" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C4759" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4760" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4760" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4760" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4761" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4761" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4761" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4762" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4762" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4762" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4762" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="4763" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4763" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4763" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4763" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4764" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4764" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4764" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4764" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4765" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4765" s="7">
+        <v>50</v>
+      </c>
+      <c r="C4765" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4766" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4766" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4766" s="7">
+        <v>55</v>
+      </c>
+      <c r="C4766" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4767" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4767" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4767" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4767" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4768" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4768" s="7">
+        <v>30</v>
+      </c>
+      <c r="C4768" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4769" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4769" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4769" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4770" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4770" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4770" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4771" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4771" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4771" s="7">
+        <v>95</v>
+      </c>
+      <c r="C4771" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4772" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4772" s="7">
+        <v>57</v>
+      </c>
+      <c r="C4772" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4773" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4773" s="7">
+        <v>70</v>
+      </c>
+      <c r="C4773" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4774" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4774" s="7">
+        <v>135</v>
+      </c>
+      <c r="C4774" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4775" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4775" s="7">
+        <v>245</v>
+      </c>
+      <c r="C4775" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4776" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4776" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4776" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4777" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4777" s="7">
+        <v>24</v>
+      </c>
+      <c r="C4777" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4778" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4778" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="C4778" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4779" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4779" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4779" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4780" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4780" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4780" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4781" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4781" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4781" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4782" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4782" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4782" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4783" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4783" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4783" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4784" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4784" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4784" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4785" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4785" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4785" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4786" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4786" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4786" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4787" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4787" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4787" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4788" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4788" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4788" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4789" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4789" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4789" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4790" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4790" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4790" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4791" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4791" s="7">
+        <v>28</v>
+      </c>
+      <c r="C4791" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4792" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4792" s="7">
+        <v>29</v>
+      </c>
+      <c r="C4792" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4793" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4793" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4793" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4794" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4794" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4794" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4795" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4795" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4795" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4796" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4796" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4796" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4797" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4797" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4797" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4798" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4798" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4798" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4799" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4799" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4799" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C4799" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4800" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4800" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4800" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4801" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4801" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4801" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4802" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4802" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4802" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4803" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4803" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C4803" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4804" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4804" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4804" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4805" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4805" s="7">
+        <v>85</v>
+      </c>
+      <c r="C4805" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4806" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4806" s="7">
+        <v>85</v>
+      </c>
+      <c r="C4806" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4807" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4807" s="7">
+        <v>90</v>
+      </c>
+      <c r="C4807" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4808" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4808" s="7">
+        <v>105</v>
+      </c>
+      <c r="C4808" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4809" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4809" s="7">
+        <v>130</v>
+      </c>
+      <c r="C4809" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4810" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4810" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4810" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4811" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4811" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4811" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4812" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4812" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4812" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4813" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4813" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4813" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4814" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4814" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4814" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4814" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4815" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4815" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4815" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4815" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4816" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4816" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4816" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C4816" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4817" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4817" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4817" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4818" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4818" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4818" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4819" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4819" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4819" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4820" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4820" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4820" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4820" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4821" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4821" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4821" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4822" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4822" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4822" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4822" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4823" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4823" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4823" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4823" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4824" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4824" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4824" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4825" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4825" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4825" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4826" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4826" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4826" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4826" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4827" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4827" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4827" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4827" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4828" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4828" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4828" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4828" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4829" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4829" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4829" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4829" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4830" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4830" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4830" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4830" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4831" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4831" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4831" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4831" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4832" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4832" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4832" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4833" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4833" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4833" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4833" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4834" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4834" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4834" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4834" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4835" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4835" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4835" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4835" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4836" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4836" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4836" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4836" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4837" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4837" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4837" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4837" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4838" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4838" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4838" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4838" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4839" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4839" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4839" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4839" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4840" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4840" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4840" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4841" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4841" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4841" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4841" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4842" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4842" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4842" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4843" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4843" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4843" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4844" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4844" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4844" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4845" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4845" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4845" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4846" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4846" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4846" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4847" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4847" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4847" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4848" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4848" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4848" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4849" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4849" s="7">
+        <v>27</v>
+      </c>
+      <c r="C4849" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4850" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4850" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4850" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4850" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4851" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4851" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4851" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4852" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4852" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4852" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4852" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4853" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4853" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4853" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4854" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4854" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4854" s="7">
+        <v>26</v>
+      </c>
+      <c r="C4854" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4855" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4855" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C4855" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4856" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4856" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4856" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4857" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4857" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4857" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4858" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4858" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4858" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4859" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4859" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4859" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4860" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4860" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4860" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4861" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4861" s="7">
+        <v>65</v>
+      </c>
+      <c r="C4861" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4862" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4862" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4862" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4862" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4863" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4863" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4863" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4863" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4864" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4864" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4864" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4864" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4865" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4865" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4865" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4866" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4866" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4866" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4867" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4867" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4867" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4868" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4868" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4868" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4868" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4869" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4869" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4869" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4870" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4870" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4870" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4870" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4871" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4871" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4871" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4871" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4872" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4872" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4872" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4873" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4873" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4873" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4874" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4874" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4874" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4875" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4875" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4875" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4875" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4876" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4876" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4876" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4877" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4877" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4877" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4877" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4878" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4878" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4878" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4878" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4879" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4879" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4879" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4880" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4880" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4880" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4881" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4881" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4881" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4882" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4882" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4882" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4882" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4883" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4883" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4883" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4884" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4884" s="7">
+        <v>23</v>
+      </c>
+      <c r="C4884" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4885" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4885" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4885" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4886" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4886" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4886" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4887" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4887" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4887" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4887" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4888" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4888" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4888" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4888" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4889" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4889" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4889" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4890" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4890" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4890" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4891" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4891" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4891" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4892" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4892" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4892" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4892" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4893" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4893" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4893" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4894" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4894" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4894" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4894" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4895" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4895" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4895" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4895" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4896" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4896" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4896" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4897" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4897" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4897" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4898" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4898" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4898" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4899" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4899" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4899" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4900" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4900" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4900" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4900" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4901" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4901" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C4901" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4902" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4902" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4902" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4903" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4903" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4903" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4904" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4904" s="7">
+        <v>36.5</v>
+      </c>
+      <c r="C4904" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4905" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4905" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4905" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4906" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4906" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4906" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4907" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4907" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4907" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4908" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4908" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4908" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4909" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4909" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4909" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="C4909" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4910" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4910" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4910" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4911" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4911" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C4911" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4912" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4912" s="7">
+        <v>11</v>
+      </c>
+      <c r="C4912" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4913" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4913" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4913" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4914" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4914" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4914" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4915" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4915" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4915" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4916" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4916" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4916" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4917" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4917" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C4917" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4918" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4918" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C4918" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4919" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4919" s="7">
+        <v>22</v>
+      </c>
+      <c r="C4919" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4920" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4920" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4920" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4920" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4921" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4921" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4921" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4922" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4922" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4922" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4922" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4923" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4923" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4923" s="7">
+        <v>27</v>
+      </c>
+      <c r="C4923" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4924" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4924" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4924" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4924" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4925" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4925" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4925" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4925" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4926" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4926" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4926" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C4926" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4927" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4927" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4927" s="7">
+        <v>20</v>
+      </c>
+      <c r="C4927" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4928" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4928" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4928" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4928" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4929" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4929" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4929" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4929" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4930" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4930" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4930" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4930" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4931" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4931" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4931" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4931" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4932" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4932" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4932" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4932" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4933" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4933" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4933" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4933" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4934" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4934" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4934" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4934" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4935" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4935" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4935" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4935" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4936" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4936" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4936" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4936" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4937" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4937" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4937" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4937" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4938" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4938" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4938" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4938" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4939" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4939" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4939" s="7">
+        <v>28</v>
+      </c>
+      <c r="C4939" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4940" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4940" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4940" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4940" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4941" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4941" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4941" s="7">
+        <v>18</v>
+      </c>
+      <c r="C4941" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4942" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4942" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4942" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="C4942" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4943" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4943" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4943" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4944" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4944" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4944" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4945" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4945" s="7">
+        <v>75</v>
+      </c>
+      <c r="C4945" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4946" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4946" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4946" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4947" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4947" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4947" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4948" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4948" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4948" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4949" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4949" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4949" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4950" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4950" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4950" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4951" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4951" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4951" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C4951" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4952" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4952" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C4952" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4953" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4953" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4953" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4954" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4954" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4954" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4955" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4955" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4955" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4956" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4956" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4956" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4957" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4957" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4957" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4958" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4958" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C4958" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4959" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4959" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4959" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4960" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4960" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4960" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4961" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4961" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4961" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4962" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4962" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4962" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4963" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4963" s="7">
+        <v>17</v>
+      </c>
+      <c r="C4963" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4964" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4964" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4964" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4965" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4965" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4965" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4966" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4966" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C4966" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4967" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4967" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4967" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4968" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4968" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4968" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4969" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4969" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4969" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4970" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4970" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4970" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4971" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4971" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4971" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4972" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4972" s="7">
+        <v>8</v>
+      </c>
+      <c r="C4972" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4973" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4973" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C4973" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4974" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4974" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4974" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4975" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4975" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C4975" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4976" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4976" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4976" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4977" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4977" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4977" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4978" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4978" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4978" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4979" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4979" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C4979" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4980" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4980" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4980" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4981" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4981" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C4981" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4982" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4982" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="C4982" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4983" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4983" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C4983" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4984" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4984" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C4984" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4985" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4985" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4985" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4986" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4986" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4986" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4987" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4987" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4987" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4988" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4988" s="7">
+        <v>9</v>
+      </c>
+      <c r="C4988" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4989" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4989" s="7">
+        <v>16</v>
+      </c>
+      <c r="C4989" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4990" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4990" s="7">
+        <v>5</v>
+      </c>
+      <c r="C4990" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4991" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4991" s="7">
+        <v>13</v>
+      </c>
+      <c r="C4991" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4992" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4992" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4992" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4993" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4993" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C4993" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4994" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4994" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C4994" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4995" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4995" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C4995" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4996" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4996" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4996" s="7">
+        <v>21</v>
+      </c>
+      <c r="C4996" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4997" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4997" s="7">
+        <v>14</v>
+      </c>
+      <c r="C4997" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4998" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4998" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C4998" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4999" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B4999" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4999" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5000" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5000" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5000" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="C5000" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5001" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5001" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5001" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5002" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5002" s="7">
+        <v>14</v>
+      </c>
+      <c r="C5002" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5003" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5003" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5003" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5004" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5004" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C5004" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5005" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5005" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5005" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5006" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5006" s="7">
+        <v>12</v>
+      </c>
+      <c r="C5006" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5007" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5007" s="7">
+        <v>13</v>
+      </c>
+      <c r="C5007" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5008" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5008" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5008" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5008" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5009" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5009" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5009" s="7">
+        <v>13</v>
+      </c>
+      <c r="C5009" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5010" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5010" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5010" s="7">
+        <v>12</v>
+      </c>
+      <c r="C5010" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5011" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5011" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5011" s="7">
+        <v>10</v>
+      </c>
+      <c r="C5011" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5012" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5012" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5012" s="7">
+        <v>35</v>
+      </c>
+      <c r="C5012" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5013" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5013" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5013" s="7">
+        <v>16</v>
+      </c>
+      <c r="C5013" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5014" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5014" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5014" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5014" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5015" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5015" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5015" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="C5015" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5016" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5016" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5016" s="7">
+        <v>30</v>
+      </c>
+      <c r="C5016" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5017" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5017" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5017" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5018" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5018" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5018" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5018" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5019" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5019" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5019" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5020" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5020" s="7">
+        <v>2</v>
+      </c>
+      <c r="C5020" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5021" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5021" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5021" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5022" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5022" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5022" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C5022" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5023" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5023" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="C5023" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5024" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5024" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C5024" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5025" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5025" s="7">
+        <v>6</v>
+      </c>
+      <c r="C5025" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5026" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5026" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5026" s="7">
+        <v>12</v>
+      </c>
+      <c r="C5026" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5027" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5027" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5027" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5027" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5028" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5028" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C5028" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5029" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5029" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5029" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5029" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5030" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5030" s="7">
+        <v>0</v>
+      </c>
+      <c r="C5030" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5031" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5031" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5031" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="C5031" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5032" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5032" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5032" s="7">
+        <v>60</v>
+      </c>
+      <c r="C5032" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5033" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5033" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5033" s="7">
+        <v>45</v>
+      </c>
+      <c r="C5033" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5034" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5034" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5034" s="7">
+        <v>32</v>
+      </c>
+      <c r="C5034" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5035" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5035" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5035" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5035" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5036" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5036" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5036" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5036" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5037" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5037" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5037" s="7">
+        <v>75</v>
+      </c>
+      <c r="C5037" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5038" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5038" s="7">
+        <v>110</v>
+      </c>
+      <c r="C5038" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5039" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5039" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5039" s="7">
+        <v>28</v>
+      </c>
+      <c r="C5039" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5040" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5040" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5040" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C5040" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5041" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5041" s="7">
+        <v>125</v>
+      </c>
+      <c r="C5041" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5042" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5042" s="7">
+        <v>90</v>
+      </c>
+      <c r="C5042" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5043" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5043" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5043" s="7">
+        <v>19</v>
+      </c>
+      <c r="C5043" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5044" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5044" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5044" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C5044" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5045" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5045" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5045" s="7">
+        <v>21</v>
+      </c>
+      <c r="C5045" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5046" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5046" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5046" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5046" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5047" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5047" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5047" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C5047" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5048" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5048" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5048" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5048" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5049" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5049" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5049" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C5049" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5050" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5050" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5050" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5050" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5051" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5051" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5051" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C5051" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5052" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5052" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5052" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C5052" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5053" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5053" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5053" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5053" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5054" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5054" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5054" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5054" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5055" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5055" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5055" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C5055" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5056" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5056" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5056" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C5056" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5057" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5057" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5057" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C5057" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5058" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5058" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5058" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C5058" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5059" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5059" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5059" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5059" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5060" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5060" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5060" s="7">
+        <v>45</v>
+      </c>
+      <c r="C5060" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5061" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5061" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5061" s="7">
+        <v>95</v>
+      </c>
+      <c r="C5061" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5062" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5062" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5062" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C5062" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5063" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5063" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5063" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5063" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5064" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5064" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5064" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5064" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5065" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5065" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5065" s="7">
+        <v>4</v>
+      </c>
+      <c r="C5065" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5066" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5066" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5066" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5066" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5067" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5067" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5067" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5067" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5068" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5068" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5068" s="7">
+        <v>18</v>
+      </c>
+      <c r="C5068" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5069" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5069" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5069" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C5069" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="5070" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5070" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5070" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C5070" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="5071" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5071" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5071" s="7">
+        <v>11</v>
+      </c>
+      <c r="C5071" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5072" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5072" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5072" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5072" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5073" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5073" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5073" s="7">
+        <v>21</v>
+      </c>
+      <c r="C5073" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5074" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5074" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5074" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5074" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5075" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5075" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5075" s="7">
+        <v>45</v>
+      </c>
+      <c r="C5075" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5076" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5076" s="7">
+        <v>25</v>
+      </c>
+      <c r="C5076" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5077" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5077" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5077" s="7">
+        <v>85</v>
+      </c>
+      <c r="C5077" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5078" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5078" s="7">
+        <v>80</v>
+      </c>
+      <c r="C5078" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5079" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5079" s="7">
+        <v>125</v>
+      </c>
+      <c r="C5079" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5080" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5080" s="7">
+        <v>85</v>
+      </c>
+      <c r="C5080" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5081" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5081" s="7">
+        <v>55</v>
+      </c>
+      <c r="C5081" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5082" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5082" s="7">
+        <v>50</v>
+      </c>
+      <c r="C5082" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5083" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5083" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5083" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5084" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5084" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C5084" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5085" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5085" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5085" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5085" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5086" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5086" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5086" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5087" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5087" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C5087" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5088" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5088" s="7">
+        <v>45</v>
+      </c>
+      <c r="C5088" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5089" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5089" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C5089" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5090" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5090" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C5090" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5091" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5091" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C5091" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5092" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5092" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5092" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5093" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5093" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5093" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="5094" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5094" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5094" s="7">
+        <v>6</v>
+      </c>
+      <c r="C5094" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5095" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5095" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C5095" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5096" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5096" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5096" s="7">
+        <v>11</v>
+      </c>
+      <c r="C5096" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5097" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5097" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5097" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5097" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5098" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5098" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5098" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5098" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5099" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5099" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5099" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C5099" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5100" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5100" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C5100" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5101" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5101" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5101" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5102" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5102" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5102" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5103" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5103" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="C5103" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5104" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5104" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C5104" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5105" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5105" s="7">
+        <v>13</v>
+      </c>
+      <c r="C5105" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5106" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5106" s="7">
+        <v>35</v>
+      </c>
+      <c r="C5106" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5107" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5107" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5107" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5108" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5108" s="7">
+        <v>25</v>
+      </c>
+      <c r="C5108" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5109" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5109" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C5109" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5110" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5110" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5110" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5111" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5111" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="C5111" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5112" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5112" s="7">
+        <v>15</v>
+      </c>
+      <c r="C5112" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5113" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5113" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5113" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5114" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5114" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5114" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5115" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5115" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5115" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5116" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5116" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5116" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5117" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5117" s="7">
+        <v>34</v>
+      </c>
+      <c r="C5117" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5118" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5118" s="7">
+        <v>13</v>
+      </c>
+      <c r="C5118" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5119" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5119" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5119" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5120" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5120" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5120" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5121" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5121" s="7">
+        <v>10</v>
+      </c>
+      <c r="C5121" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5122" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5122" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C5122" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5123" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5123" s="7">
+        <v>21</v>
+      </c>
+      <c r="C5123" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5124" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5124" s="7">
+        <v>6</v>
+      </c>
+      <c r="C5124" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5125" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5125" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5125" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5126" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5126" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C5126" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5127" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5127" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5127" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5128" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5128" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5128" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5129" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5129" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5129" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5130" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5130" s="7">
+        <v>6</v>
+      </c>
+      <c r="C5130" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5131" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5131" s="7">
+        <v>11</v>
+      </c>
+      <c r="C5131" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5132" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5132" s="7">
+        <v>17</v>
+      </c>
+      <c r="C5132" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5133" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5133" s="7">
+        <v>34</v>
+      </c>
+      <c r="C5133" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5134" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5134" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C5134" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5135" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5135" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5135" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5136" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5136" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C5136" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5137" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5137" s="7">
+        <v>14</v>
+      </c>
+      <c r="C5137" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5138" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5138" s="7">
+        <v>65</v>
+      </c>
+      <c r="C5138" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5139" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5139" s="7">
+        <v>50</v>
+      </c>
+      <c r="C5139" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5140" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5140" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="C5140" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5141" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5141" s="7">
+        <v>12</v>
+      </c>
+      <c r="C5141" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5142" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5142" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5142" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5143" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5143" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="C5143" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5144" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5144" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C5144" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5145" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5145" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5145" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5146" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5146" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="C5146" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5147" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5147" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5147" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5148" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5148" s="7">
+        <v>16</v>
+      </c>
+      <c r="C5148" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="5149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5149" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5149" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C5149" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5150" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5150" s="7">
+        <v>4</v>
+      </c>
+      <c r="C5150" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5151" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5151" s="7">
+        <v>10</v>
+      </c>
+      <c r="C5151" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5152" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5152" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="C5152" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5153" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5153" s="7">
+        <v>8</v>
+      </c>
+      <c r="C5153" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5154" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5154" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="C5154" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5155" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5155" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C5155" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5156" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5156" s="7">
+        <v>8</v>
+      </c>
+      <c r="C5156" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5157" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5157" s="7">
+        <v>31</v>
+      </c>
+      <c r="C5157" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5158" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5158" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="C5158" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5159" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5159" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5159" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5160" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5160" s="7">
+        <v>5</v>
+      </c>
+      <c r="C5160" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5161" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5161" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="C5161" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5162" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5162" s="7">
+        <v>12</v>
+      </c>
+      <c r="C5162" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5163" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5163" s="7">
+        <v>7</v>
+      </c>
+      <c r="C5163" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="5164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5164" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5164" s="7">
+        <v>15</v>
+      </c>
+      <c r="C5164" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5165" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5165" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="C5165" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5166" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B5166" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5166" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C4370">
+  <conditionalFormatting sqref="C2:C5166">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanaKralikova\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE52D29F-632A-44B1-8AAD-A4497EC2A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ACD6CC-3E38-45A1-A299-DF19E39EFF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E01B0AB-BD68-4F76-B5AA-846182E56997}"/>
   </bookViews>
@@ -2320,9 +2320,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}" name="Tabuľka1" displayName="Tabuľka1" ref="A1:C5166" totalsRowShown="0">
   <autoFilter ref="A1:C5166" xr:uid="{79A64048-39A7-4EA6-99E0-CE1157777D2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C999">
-    <sortCondition ref="A1:A999"/>
-  </sortState>
   <tableColumns count="3">
     <tableColumn id="4" xr3:uid="{ADF7FDBC-1C20-47ED-8A60-FCEB998DB62C}" name="Dátum zvozu" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{2105C53A-A455-4B66-A74F-6750BD5FC4B5}" name="Počet kg odpadu" dataDxfId="3"/>
@@ -56482,7 +56479,7 @@
     </row>
     <row r="4894" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4894" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4894" s="7">
         <v>6</v>
@@ -56493,7 +56490,7 @@
     </row>
     <row r="4895" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4895" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4895" s="7">
         <v>12.5</v>
@@ -56504,7 +56501,7 @@
     </row>
     <row r="4896" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4896" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4896" s="7">
         <v>15.5</v>
@@ -56515,7 +56512,7 @@
     </row>
     <row r="4897" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4897" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4897" s="7">
         <v>7.5</v>
@@ -56526,7 +56523,7 @@
     </row>
     <row r="4898" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4898" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4898" s="7">
         <v>7.5</v>
@@ -56537,7 +56534,7 @@
     </row>
     <row r="4899" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4899" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4899" s="7">
         <v>7</v>
@@ -56548,7 +56545,7 @@
     </row>
     <row r="4900" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4900" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4900" s="7">
         <v>22.5</v>
@@ -56559,7 +56556,7 @@
     </row>
     <row r="4901" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4901" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4901" s="7">
         <v>14.5</v>
@@ -56570,7 +56567,7 @@
     </row>
     <row r="4902" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4902" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4902" s="7">
         <v>16</v>
@@ -56581,7 +56578,7 @@
     </row>
     <row r="4903" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4903" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4903" s="7">
         <v>17.5</v>
@@ -56592,7 +56589,7 @@
     </row>
     <row r="4904" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4904" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4904" s="7">
         <v>36.5</v>
@@ -56603,7 +56600,7 @@
     </row>
     <row r="4905" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4905" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4905" s="7">
         <v>7</v>
@@ -56614,7 +56611,7 @@
     </row>
     <row r="4906" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4906" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4906" s="7">
         <v>6.5</v>
@@ -56625,7 +56622,7 @@
     </row>
     <row r="4907" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4907" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4907" s="7">
         <v>9</v>
@@ -56636,7 +56633,7 @@
     </row>
     <row r="4908" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4908" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4908" s="7">
         <v>12</v>
@@ -56647,7 +56644,7 @@
     </row>
     <row r="4909" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4909" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4909" s="7">
         <v>29.5</v>
@@ -56658,7 +56655,7 @@
     </row>
     <row r="4910" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4910" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4910" s="7">
         <v>18</v>
@@ -56669,7 +56666,7 @@
     </row>
     <row r="4911" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4911" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4911" s="7">
         <v>32.5</v>
@@ -56680,7 +56677,7 @@
     </row>
     <row r="4912" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4912" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4912" s="7">
         <v>11</v>
@@ -56691,7 +56688,7 @@
     </row>
     <row r="4913" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4913" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4913" s="7">
         <v>10.5</v>
@@ -56702,7 +56699,7 @@
     </row>
     <row r="4914" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4914" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4914" s="7">
         <v>5.5</v>
@@ -56713,7 +56710,7 @@
     </row>
     <row r="4915" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4915" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4915" s="7">
         <v>10</v>
@@ -56724,7 +56721,7 @@
     </row>
     <row r="4916" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4916" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4916" s="7">
         <v>6</v>
@@ -56735,7 +56732,7 @@
     </row>
     <row r="4917" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4917" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4917" s="7">
         <v>5.5</v>
@@ -56746,7 +56743,7 @@
     </row>
     <row r="4918" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4918" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4918" s="7">
         <v>30.5</v>
@@ -56757,7 +56754,7 @@
     </row>
     <row r="4919" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4919" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4919" s="7">
         <v>22</v>
@@ -56768,7 +56765,7 @@
     </row>
     <row r="4920" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4920" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4920" s="7">
         <v>3.5</v>
@@ -56779,7 +56776,7 @@
     </row>
     <row r="4921" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4921" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4921" s="7">
         <v>19</v>
@@ -56790,7 +56787,7 @@
     </row>
     <row r="4922" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4922" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4922" s="7">
         <v>21</v>
@@ -56801,7 +56798,7 @@
     </row>
     <row r="4923" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4923" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4923" s="7">
         <v>27</v>
@@ -56812,7 +56809,7 @@
     </row>
     <row r="4924" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4924" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4924" s="7">
         <v>16.5</v>
@@ -56823,7 +56820,7 @@
     </row>
     <row r="4925" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4925" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4925" s="7">
         <v>13</v>
@@ -56834,7 +56831,7 @@
     </row>
     <row r="4926" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4926" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4926" s="7">
         <v>3.5</v>
@@ -56845,7 +56842,7 @@
     </row>
     <row r="4927" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4927" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4927" s="7">
         <v>20</v>
@@ -56856,7 +56853,7 @@
     </row>
     <row r="4928" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4928" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4928" s="7">
         <v>4.5</v>
@@ -56867,7 +56864,7 @@
     </row>
     <row r="4929" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4929" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4929" s="7">
         <v>16</v>
@@ -56878,7 +56875,7 @@
     </row>
     <row r="4930" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4930" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4930" s="7">
         <v>12.5</v>
@@ -56889,7 +56886,7 @@
     </row>
     <row r="4931" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4931" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4931" s="7">
         <v>10</v>
@@ -56900,7 +56897,7 @@
     </row>
     <row r="4932" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4932" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4932" s="7">
         <v>19</v>
@@ -56911,7 +56908,7 @@
     </row>
     <row r="4933" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4933" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4933" s="7">
         <v>7</v>
@@ -56922,7 +56919,7 @@
     </row>
     <row r="4934" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4934" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4934" s="7">
         <v>10.5</v>
@@ -56933,7 +56930,7 @@
     </row>
     <row r="4935" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4935" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4935" s="7">
         <v>17.5</v>
@@ -56944,7 +56941,7 @@
     </row>
     <row r="4936" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4936" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4936" s="7">
         <v>15.5</v>
@@ -56955,7 +56952,7 @@
     </row>
     <row r="4937" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4937" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4937" s="7">
         <v>5</v>
@@ -56966,7 +56963,7 @@
     </row>
     <row r="4938" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4938" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4938" s="7">
         <v>13</v>
@@ -56977,7 +56974,7 @@
     </row>
     <row r="4939" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4939" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4939" s="7">
         <v>28</v>
@@ -56988,7 +56985,7 @@
     </row>
     <row r="4940" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4940" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4940" s="7">
         <v>14</v>
@@ -56999,7 +56996,7 @@
     </row>
     <row r="4941" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4941" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4941" s="7">
         <v>18</v>
@@ -57010,7 +57007,7 @@
     </row>
     <row r="4942" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4942" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4942" s="7">
         <v>26.5</v>
@@ -57021,7 +57018,7 @@
     </row>
     <row r="4943" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4943" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4943" s="7">
         <v>10</v>
@@ -57032,7 +57029,7 @@
     </row>
     <row r="4944" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4944" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4944" s="7">
         <v>9</v>
@@ -57043,7 +57040,7 @@
     </row>
     <row r="4945" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4945" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4945" s="7">
         <v>75</v>
@@ -57054,7 +57051,7 @@
     </row>
     <row r="4946" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4946" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4946" s="7">
         <v>21</v>
@@ -57065,7 +57062,7 @@
     </row>
     <row r="4947" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4947" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4947" s="7">
         <v>16.5</v>
@@ -57076,7 +57073,7 @@
     </row>
     <row r="4948" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4948" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4948" s="7">
         <v>9</v>
@@ -57087,7 +57084,7 @@
     </row>
     <row r="4949" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4949" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4949" s="7">
         <v>16.5</v>
@@ -57098,7 +57095,7 @@
     </row>
     <row r="4950" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4950" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4950" s="7">
         <v>7.5</v>
@@ -57109,7 +57106,7 @@
     </row>
     <row r="4951" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4951" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4951" s="7">
         <v>24.5</v>
@@ -57120,7 +57117,7 @@
     </row>
     <row r="4952" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4952" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4952" s="7">
         <v>15.5</v>
@@ -57131,7 +57128,7 @@
     </row>
     <row r="4953" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4953" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4953" s="7">
         <v>14</v>
@@ -57142,7 +57139,7 @@
     </row>
     <row r="4954" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4954" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4954" s="7">
         <v>16</v>
@@ -57153,7 +57150,7 @@
     </row>
     <row r="4955" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4955" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4955" s="7">
         <v>12</v>
@@ -57164,7 +57161,7 @@
     </row>
     <row r="4956" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4956" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4956" s="7">
         <v>15</v>
@@ -57175,7 +57172,7 @@
     </row>
     <row r="4957" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4957" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4957" s="7">
         <v>19.5</v>
@@ -57186,7 +57183,7 @@
     </row>
     <row r="4958" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4958" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4958" s="7">
         <v>12.5</v>
@@ -57197,7 +57194,7 @@
     </row>
     <row r="4959" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4959" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4959" s="7">
         <v>7.5</v>
@@ -57208,7 +57205,7 @@
     </row>
     <row r="4960" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4960" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4960" s="7">
         <v>16</v>
@@ -57219,7 +57216,7 @@
     </row>
     <row r="4961" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4961" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4961" s="7">
         <v>6</v>
@@ -57230,7 +57227,7 @@
     </row>
     <row r="4962" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4962" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4962" s="7">
         <v>1.5</v>
@@ -57241,7 +57238,7 @@
     </row>
     <row r="4963" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4963" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4963" s="7">
         <v>17</v>
@@ -57252,7 +57249,7 @@
     </row>
     <row r="4964" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4964" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4964" s="7">
         <v>11.5</v>
@@ -57263,7 +57260,7 @@
     </row>
     <row r="4965" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4965" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4965" s="7">
         <v>8</v>
@@ -57274,7 +57271,7 @@
     </row>
     <row r="4966" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4966" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4966" s="7">
         <v>10.5</v>
@@ -57285,7 +57282,7 @@
     </row>
     <row r="4967" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4967" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4967" s="7">
         <v>13.5</v>
@@ -57296,7 +57293,7 @@
     </row>
     <row r="4968" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4968" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4968" s="7">
         <v>9</v>
@@ -57307,7 +57304,7 @@
     </row>
     <row r="4969" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4969" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4969" s="7">
         <v>4</v>
@@ -57318,7 +57315,7 @@
     </row>
     <row r="4970" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4970" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4970" s="7">
         <v>8.5</v>
@@ -57329,7 +57326,7 @@
     </row>
     <row r="4971" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4971" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4971" s="7">
         <v>12</v>
@@ -57340,7 +57337,7 @@
     </row>
     <row r="4972" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4972" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4972" s="7">
         <v>8</v>
@@ -57351,7 +57348,7 @@
     </row>
     <row r="4973" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4973" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4973" s="7">
         <v>16.5</v>
@@ -57362,7 +57359,7 @@
     </row>
     <row r="4974" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4974" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4974" s="7">
         <v>9</v>
@@ -57373,7 +57370,7 @@
     </row>
     <row r="4975" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4975" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4975" s="7">
         <v>4.5</v>
@@ -57384,7 +57381,7 @@
     </row>
     <row r="4976" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4976" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4976" s="7">
         <v>9</v>
@@ -57395,7 +57392,7 @@
     </row>
     <row r="4977" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4977" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4977" s="7">
         <v>9</v>
@@ -57406,7 +57403,7 @@
     </row>
     <row r="4978" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4978" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4978" s="7">
         <v>6.5</v>
@@ -57417,7 +57414,7 @@
     </row>
     <row r="4979" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4979" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4979" s="7">
         <v>9.5</v>
@@ -57428,7 +57425,7 @@
     </row>
     <row r="4980" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4980" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4980" s="7">
         <v>7.5</v>
@@ -57439,7 +57436,7 @@
     </row>
     <row r="4981" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4981" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4981" s="7">
         <v>8.5</v>
@@ -57450,7 +57447,7 @@
     </row>
     <row r="4982" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4982" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4982" s="7">
         <v>22.5</v>
@@ -57461,7 +57458,7 @@
     </row>
     <row r="4983" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4983" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4983" s="7">
         <v>6.5</v>
@@ -57472,7 +57469,7 @@
     </row>
     <row r="4984" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4984" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4984" s="7">
         <v>17.5</v>
@@ -57483,7 +57480,7 @@
     </row>
     <row r="4985" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4985" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4985" s="7">
         <v>7</v>
@@ -57494,7 +57491,7 @@
     </row>
     <row r="4986" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4986" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4986" s="7">
         <v>6</v>
@@ -57505,7 +57502,7 @@
     </row>
     <row r="4987" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4987" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4987" s="7">
         <v>13.5</v>
@@ -57516,7 +57513,7 @@
     </row>
     <row r="4988" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4988" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4988" s="7">
         <v>9</v>
@@ -57527,7 +57524,7 @@
     </row>
     <row r="4989" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4989" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4989" s="7">
         <v>16</v>
@@ -57538,7 +57535,7 @@
     </row>
     <row r="4990" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4990" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4990" s="7">
         <v>5</v>
@@ -57549,7 +57546,7 @@
     </row>
     <row r="4991" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4991" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4991" s="7">
         <v>13</v>
@@ -57560,7 +57557,7 @@
     </row>
     <row r="4992" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4992" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4992" s="7">
         <v>11.5</v>
@@ -57571,7 +57568,7 @@
     </row>
     <row r="4993" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4993" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4993" s="7">
         <v>19.5</v>
@@ -57582,7 +57579,7 @@
     </row>
     <row r="4994" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4994" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4994" s="7">
         <v>7.5</v>
@@ -57593,7 +57590,7 @@
     </row>
     <row r="4995" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4995" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4995" s="7">
         <v>11.5</v>
@@ -57604,7 +57601,7 @@
     </row>
     <row r="4996" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4996" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4996" s="7">
         <v>21</v>
@@ -57615,7 +57612,7 @@
     </row>
     <row r="4997" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4997" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4997" s="7">
         <v>14</v>
@@ -57626,7 +57623,7 @@
     </row>
     <row r="4998" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4998" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4998" s="7">
         <v>13.5</v>
@@ -57637,7 +57634,7 @@
     </row>
     <row r="4999" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4999" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B4999" s="7">
         <v>10</v>
@@ -57648,7 +57645,7 @@
     </row>
     <row r="5000" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5000" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5000" s="7">
         <v>32.5</v>
@@ -57659,7 +57656,7 @@
     </row>
     <row r="5001" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5001" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5001" s="7">
         <v>6.5</v>
@@ -57670,7 +57667,7 @@
     </row>
     <row r="5002" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5002" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5002" s="7">
         <v>14</v>
@@ -57681,7 +57678,7 @@
     </row>
     <row r="5003" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5003" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5003" s="7">
         <v>5</v>
@@ -57692,7 +57689,7 @@
     </row>
     <row r="5004" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5004" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5004" s="7">
         <v>4.5</v>
@@ -57703,7 +57700,7 @@
     </row>
     <row r="5005" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5005" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5005" s="7">
         <v>9.5</v>
@@ -57714,7 +57711,7 @@
     </row>
     <row r="5006" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5006" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5006" s="7">
         <v>12</v>
@@ -57725,7 +57722,7 @@
     </row>
     <row r="5007" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5007" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5007" s="7">
         <v>13</v>
@@ -57736,7 +57733,7 @@
     </row>
     <row r="5008" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5008" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5008" s="7">
         <v>6.5</v>
@@ -57747,7 +57744,7 @@
     </row>
     <row r="5009" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5009" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5009" s="7">
         <v>13</v>
@@ -57758,7 +57755,7 @@
     </row>
     <row r="5010" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5010" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5010" s="7">
         <v>12</v>
@@ -57769,7 +57766,7 @@
     </row>
     <row r="5011" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5011" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5011" s="7">
         <v>10</v>
@@ -57780,7 +57777,7 @@
     </row>
     <row r="5012" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5012" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5012" s="7">
         <v>35</v>
@@ -57791,7 +57788,7 @@
     </row>
     <row r="5013" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5013" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5013" s="7">
         <v>16</v>
@@ -57802,7 +57799,7 @@
     </row>
     <row r="5014" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5014" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5014" s="7">
         <v>9</v>
@@ -57813,7 +57810,7 @@
     </row>
     <row r="5015" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5015" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5015" s="7">
         <v>33.5</v>
@@ -57824,7 +57821,7 @@
     </row>
     <row r="5016" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5016" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5016" s="7">
         <v>30</v>
@@ -57835,7 +57832,7 @@
     </row>
     <row r="5017" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5017" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5017" s="7">
         <v>9.5</v>
@@ -57846,7 +57843,7 @@
     </row>
     <row r="5018" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5018" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5018" s="7">
         <v>8.5</v>
@@ -57857,7 +57854,7 @@
     </row>
     <row r="5019" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5019" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5019" s="7">
         <v>5</v>
@@ -57868,7 +57865,7 @@
     </row>
     <row r="5020" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5020" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5020" s="7">
         <v>2</v>
@@ -57879,7 +57876,7 @@
     </row>
     <row r="5021" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5021" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5021" s="7">
         <v>6.5</v>
@@ -57890,7 +57887,7 @@
     </row>
     <row r="5022" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5022" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5022" s="7">
         <v>13.5</v>
@@ -57901,7 +57898,7 @@
     </row>
     <row r="5023" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5023" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5023" s="7">
         <v>5.5</v>
@@ -57912,7 +57909,7 @@
     </row>
     <row r="5024" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5024" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5024" s="7">
         <v>15.5</v>
@@ -57923,7 +57920,7 @@
     </row>
     <row r="5025" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5025" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5025" s="7">
         <v>6</v>
@@ -57934,7 +57931,7 @@
     </row>
     <row r="5026" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5026" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5026" s="7">
         <v>12</v>
@@ -57945,7 +57942,7 @@
     </row>
     <row r="5027" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5027" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5027" s="7">
         <v>7.5</v>
@@ -57956,7 +57953,7 @@
     </row>
     <row r="5028" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5028" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5028" s="7">
         <v>18.5</v>
@@ -57967,7 +57964,7 @@
     </row>
     <row r="5029" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5029" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5029" s="7">
         <v>5</v>
@@ -57978,7 +57975,7 @@
     </row>
     <row r="5030" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5030" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5030" s="7">
         <v>0</v>
@@ -57989,7 +57986,7 @@
     </row>
     <row r="5031" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5031" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5031" s="7">
         <v>24.5</v>
@@ -58000,7 +57997,7 @@
     </row>
     <row r="5032" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5032" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5032" s="7">
         <v>60</v>
@@ -58011,7 +58008,7 @@
     </row>
     <row r="5033" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5033" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5033" s="7">
         <v>45</v>
@@ -58022,7 +58019,7 @@
     </row>
     <row r="5034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5034" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5034" s="7">
         <v>32</v>
@@ -58033,7 +58030,7 @@
     </row>
     <row r="5035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5035" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5035" s="7">
         <v>7.5</v>
@@ -58044,7 +58041,7 @@
     </row>
     <row r="5036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5036" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5036" s="7">
         <v>14.5</v>
@@ -58055,7 +58052,7 @@
     </row>
     <row r="5037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5037" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5037" s="7">
         <v>75</v>
@@ -58066,7 +58063,7 @@
     </row>
     <row r="5038" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5038" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5038" s="7">
         <v>110</v>
@@ -58077,7 +58074,7 @@
     </row>
     <row r="5039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5039" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5039" s="7">
         <v>28</v>
@@ -58088,7 +58085,7 @@
     </row>
     <row r="5040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5040" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5040" s="7">
         <v>23.5</v>
@@ -58099,7 +58096,7 @@
     </row>
     <row r="5041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5041" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5041" s="7">
         <v>125</v>
@@ -58110,7 +58107,7 @@
     </row>
     <row r="5042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5042" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5042" s="7">
         <v>90</v>
@@ -58121,7 +58118,7 @@
     </row>
     <row r="5043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5043" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5043" s="7">
         <v>19</v>
@@ -58132,7 +58129,7 @@
     </row>
     <row r="5044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5044" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5044" s="7">
         <v>16.5</v>
@@ -58143,7 +58140,7 @@
     </row>
     <row r="5045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5045" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5045" s="7">
         <v>21</v>
@@ -58154,7 +58151,7 @@
     </row>
     <row r="5046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5046" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5046" s="7">
         <v>7.5</v>
@@ -58165,7 +58162,7 @@
     </row>
     <row r="5047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5047" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5047" s="7">
         <v>12.5</v>
@@ -58176,7 +58173,7 @@
     </row>
     <row r="5048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5048" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5048" s="7">
         <v>7</v>
@@ -58187,7 +58184,7 @@
     </row>
     <row r="5049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5049" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5049" s="7">
         <v>12.5</v>
@@ -58198,7 +58195,7 @@
     </row>
     <row r="5050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5050" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5050" s="7">
         <v>20</v>
@@ -58209,7 +58206,7 @@
     </row>
     <row r="5051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5051" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5051" s="7">
         <v>11.5</v>
@@ -58220,7 +58217,7 @@
     </row>
     <row r="5052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5052" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5052" s="7">
         <v>21.5</v>
@@ -58231,7 +58228,7 @@
     </row>
     <row r="5053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5053" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5053" s="7">
         <v>9</v>
@@ -58242,7 +58239,7 @@
     </row>
     <row r="5054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5054" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5054" s="7">
         <v>8.5</v>
@@ -58253,7 +58250,7 @@
     </row>
     <row r="5055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5055" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5055" s="7">
         <v>13.5</v>
@@ -58264,7 +58261,7 @@
     </row>
     <row r="5056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5056" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5056" s="7">
         <v>11.5</v>
@@ -58275,7 +58272,7 @@
     </row>
     <row r="5057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5057" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5057" s="7">
         <v>20.5</v>
@@ -58286,7 +58283,7 @@
     </row>
     <row r="5058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5058" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5058" s="7">
         <v>13.5</v>
@@ -58297,7 +58294,7 @@
     </row>
     <row r="5059" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5059" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5059" s="7">
         <v>5</v>
@@ -58308,7 +58305,7 @@
     </row>
     <row r="5060" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5060" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5060" s="7">
         <v>45</v>
@@ -58319,7 +58316,7 @@
     </row>
     <row r="5061" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5061" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5061" s="7">
         <v>95</v>
@@ -58330,7 +58327,7 @@
     </row>
     <row r="5062" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5062" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5062" s="7">
         <v>17.5</v>
@@ -58341,7 +58338,7 @@
     </row>
     <row r="5063" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5063" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5063" s="7">
         <v>3</v>
@@ -58352,7 +58349,7 @@
     </row>
     <row r="5064" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5064" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5064" s="7">
         <v>7.5</v>
@@ -58363,7 +58360,7 @@
     </row>
     <row r="5065" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5065" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5065" s="7">
         <v>4</v>
@@ -58374,7 +58371,7 @@
     </row>
     <row r="5066" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5066" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5066" s="7">
         <v>14.5</v>
@@ -58385,7 +58382,7 @@
     </row>
     <row r="5067" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5067" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5067" s="7">
         <v>14.5</v>
@@ -58396,7 +58393,7 @@
     </row>
     <row r="5068" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5068" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5068" s="7">
         <v>18</v>
@@ -58407,7 +58404,7 @@
     </row>
     <row r="5069" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5069" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5069" s="7">
         <v>3.5</v>
@@ -58418,7 +58415,7 @@
     </row>
     <row r="5070" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5070" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5070" s="7">
         <v>12.5</v>
@@ -58429,7 +58426,7 @@
     </row>
     <row r="5071" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5071" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5071" s="7">
         <v>11</v>
@@ -58440,7 +58437,7 @@
     </row>
     <row r="5072" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5072" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5072" s="7">
         <v>5</v>
@@ -58451,7 +58448,7 @@
     </row>
     <row r="5073" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5073" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5073" s="7">
         <v>21</v>
@@ -58462,7 +58459,7 @@
     </row>
     <row r="5074" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5074" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5074" s="7">
         <v>7.5</v>
@@ -58473,7 +58470,7 @@
     </row>
     <row r="5075" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5075" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5075" s="7">
         <v>45</v>
@@ -58484,7 +58481,7 @@
     </row>
     <row r="5076" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5076" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5076" s="7">
         <v>25</v>
@@ -58495,7 +58492,7 @@
     </row>
     <row r="5077" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5077" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5077" s="7">
         <v>85</v>
@@ -58506,7 +58503,7 @@
     </row>
     <row r="5078" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5078" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5078" s="7">
         <v>80</v>
@@ -58517,7 +58514,7 @@
     </row>
     <row r="5079" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5079" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5079" s="7">
         <v>125</v>
@@ -58528,7 +58525,7 @@
     </row>
     <row r="5080" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5080" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5080" s="7">
         <v>85</v>
@@ -58539,7 +58536,7 @@
     </row>
     <row r="5081" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5081" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5081" s="7">
         <v>55</v>
@@ -58550,7 +58547,7 @@
     </row>
     <row r="5082" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5082" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5082" s="7">
         <v>50</v>
@@ -58561,7 +58558,7 @@
     </row>
     <row r="5083" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5083" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5083" s="7">
         <v>14.5</v>
@@ -58572,7 +58569,7 @@
     </row>
     <row r="5084" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5084" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5084" s="7">
         <v>15.5</v>
@@ -58583,7 +58580,7 @@
     </row>
     <row r="5085" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5085" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5085" s="7">
         <v>7</v>
@@ -58594,7 +58591,7 @@
     </row>
     <row r="5086" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5086" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5086" s="7">
         <v>9</v>
@@ -58605,7 +58602,7 @@
     </row>
     <row r="5087" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5087" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5087" s="7">
         <v>30.5</v>
@@ -58616,7 +58613,7 @@
     </row>
     <row r="5088" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5088" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5088" s="7">
         <v>45</v>
@@ -58627,7 +58624,7 @@
     </row>
     <row r="5089" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5089" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5089" s="7">
         <v>17.5</v>
@@ -58638,7 +58635,7 @@
     </row>
     <row r="5090" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5090" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5090" s="7">
         <v>12.5</v>
@@ -58649,7 +58646,7 @@
     </row>
     <row r="5091" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5091" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5091" s="7">
         <v>17.5</v>
@@ -58660,7 +58657,7 @@
     </row>
     <row r="5092" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5092" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5092" s="7">
         <v>5</v>
@@ -58671,7 +58668,7 @@
     </row>
     <row r="5093" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5093" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5093" s="7">
         <v>7</v>
@@ -58682,7 +58679,7 @@
     </row>
     <row r="5094" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5094" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5094" s="7">
         <v>6</v>
@@ -58693,7 +58690,7 @@
     </row>
     <row r="5095" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5095" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5095" s="7">
         <v>2.5</v>
@@ -58704,7 +58701,7 @@
     </row>
     <row r="5096" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5096" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5096" s="7">
         <v>11</v>
@@ -58715,7 +58712,7 @@
     </row>
     <row r="5097" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5097" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5097" s="7">
         <v>3</v>
@@ -58726,7 +58723,7 @@
     </row>
     <row r="5098" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5098" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5098" s="7">
         <v>8.5</v>
@@ -58737,7 +58734,7 @@
     </row>
     <row r="5099" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5099" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5099" s="7">
         <v>16.5</v>
@@ -58748,7 +58745,7 @@
     </row>
     <row r="5100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5100" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5100" s="7">
         <v>4.5</v>
@@ -58759,7 +58756,7 @@
     </row>
     <row r="5101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5101" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5101" s="7">
         <v>9.5</v>
@@ -58770,7 +58767,7 @@
     </row>
     <row r="5102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5102" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5102" s="7">
         <v>9.5</v>
@@ -58781,7 +58778,7 @@
     </row>
     <row r="5103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5103" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5103" s="7">
         <v>11.5</v>
@@ -58792,7 +58789,7 @@
     </row>
     <row r="5104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5104" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5104" s="7">
         <v>13.5</v>
@@ -58803,7 +58800,7 @@
     </row>
     <row r="5105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5105" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5105" s="7">
         <v>13</v>
@@ -58814,7 +58811,7 @@
     </row>
     <row r="5106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5106" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5106" s="7">
         <v>35</v>
@@ -58825,7 +58822,7 @@
     </row>
     <row r="5107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5107" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5107" s="7">
         <v>6.5</v>
@@ -58836,7 +58833,7 @@
     </row>
     <row r="5108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5108" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5108" s="7">
         <v>25</v>
@@ -58847,7 +58844,7 @@
     </row>
     <row r="5109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5109" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5109" s="7">
         <v>15.5</v>
@@ -58858,7 +58855,7 @@
     </row>
     <row r="5110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5110" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5110" s="7">
         <v>9.5</v>
@@ -58869,7 +58866,7 @@
     </row>
     <row r="5111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5111" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5111" s="7">
         <v>16.5</v>
@@ -58880,7 +58877,7 @@
     </row>
     <row r="5112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5112" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5112" s="7">
         <v>15</v>
@@ -58891,7 +58888,7 @@
     </row>
     <row r="5113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5113" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5113" s="7">
         <v>9</v>
@@ -58902,7 +58899,7 @@
     </row>
     <row r="5114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5114" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5114" s="7">
         <v>7.5</v>
@@ -58913,7 +58910,7 @@
     </row>
     <row r="5115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5115" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5115" s="7">
         <v>9.5</v>
@@ -58924,7 +58921,7 @@
     </row>
     <row r="5116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5116" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5116" s="7">
         <v>7</v>
@@ -58935,7 +58932,7 @@
     </row>
     <row r="5117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5117" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5117" s="7">
         <v>34</v>
@@ -58946,7 +58943,7 @@
     </row>
     <row r="5118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5118" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5118" s="7">
         <v>13</v>
@@ -58957,7 +58954,7 @@
     </row>
     <row r="5119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5119" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5119" s="7">
         <v>14.5</v>
@@ -58968,7 +58965,7 @@
     </row>
     <row r="5120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5120" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5120" s="7">
         <v>3</v>
@@ -58979,7 +58976,7 @@
     </row>
     <row r="5121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5121" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5121" s="7">
         <v>10</v>
@@ -58990,7 +58987,7 @@
     </row>
     <row r="5122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5122" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5122" s="7">
         <v>15.5</v>
@@ -59001,7 +58998,7 @@
     </row>
     <row r="5123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5123" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5123" s="7">
         <v>21</v>
@@ -59012,7 +59009,7 @@
     </row>
     <row r="5124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5124" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5124" s="7">
         <v>6</v>
@@ -59023,7 +59020,7 @@
     </row>
     <row r="5125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5125" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5125" s="7">
         <v>5</v>
@@ -59034,7 +59031,7 @@
     </row>
     <row r="5126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5126" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5126" s="7">
         <v>12.5</v>
@@ -59045,7 +59042,7 @@
     </row>
     <row r="5127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5127" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5127" s="7">
         <v>9.5</v>
@@ -59056,7 +59053,7 @@
     </row>
     <row r="5128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5128" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5128" s="7">
         <v>8.5</v>
@@ -59067,7 +59064,7 @@
     </row>
     <row r="5129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5129" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5129" s="7">
         <v>8.5</v>
@@ -59078,7 +59075,7 @@
     </row>
     <row r="5130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5130" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5130" s="7">
         <v>6</v>
@@ -59089,7 +59086,7 @@
     </row>
     <row r="5131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5131" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5131" s="7">
         <v>11</v>
@@ -59100,7 +59097,7 @@
     </row>
     <row r="5132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5132" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5132" s="7">
         <v>17</v>
@@ -59111,7 +59108,7 @@
     </row>
     <row r="5133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5133" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5133" s="7">
         <v>34</v>
@@ -59122,7 +59119,7 @@
     </row>
     <row r="5134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5134" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5134" s="7">
         <v>4.5</v>
@@ -59133,7 +59130,7 @@
     </row>
     <row r="5135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5135" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5135" s="7">
         <v>7</v>
@@ -59144,7 +59141,7 @@
     </row>
     <row r="5136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5136" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5136" s="7">
         <v>7.5</v>
@@ -59155,7 +59152,7 @@
     </row>
     <row r="5137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5137" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5137" s="7">
         <v>14</v>
@@ -59166,7 +59163,7 @@
     </row>
     <row r="5138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5138" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5138" s="7">
         <v>65</v>
@@ -59177,7 +59174,7 @@
     </row>
     <row r="5139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5139" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5139" s="7">
         <v>50</v>
@@ -59188,7 +59185,7 @@
     </row>
     <row r="5140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5140" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5140" s="7">
         <v>4.5</v>
@@ -59199,7 +59196,7 @@
     </row>
     <row r="5141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5141" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5141" s="7">
         <v>12</v>
@@ -59210,7 +59207,7 @@
     </row>
     <row r="5142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5142" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5142" s="7">
         <v>3</v>
@@ -59221,7 +59218,7 @@
     </row>
     <row r="5143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5143" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5143" s="7">
         <v>19.5</v>
@@ -59232,7 +59229,7 @@
     </row>
     <row r="5144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5144" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5144" s="7">
         <v>17.5</v>
@@ -59243,7 +59240,7 @@
     </row>
     <row r="5145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5145" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5145" s="7">
         <v>6.5</v>
@@ -59254,7 +59251,7 @@
     </row>
     <row r="5146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5146" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5146" s="7">
         <v>9.5</v>
@@ -59265,7 +59262,7 @@
     </row>
     <row r="5147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5147" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5147" s="7">
         <v>6.5</v>
@@ -59276,7 +59273,7 @@
     </row>
     <row r="5148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5148" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5148" s="7">
         <v>16</v>
@@ -59287,7 +59284,7 @@
     </row>
     <row r="5149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5149" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5149" s="7">
         <v>18.5</v>
@@ -59298,7 +59295,7 @@
     </row>
     <row r="5150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5150" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5150" s="7">
         <v>4</v>
@@ -59309,7 +59306,7 @@
     </row>
     <row r="5151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5151" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5151" s="7">
         <v>10</v>
@@ -59320,7 +59317,7 @@
     </row>
     <row r="5152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5152" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5152" s="7">
         <v>27.5</v>
@@ -59331,7 +59328,7 @@
     </row>
     <row r="5153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5153" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5153" s="7">
         <v>8</v>
@@ -59342,7 +59339,7 @@
     </row>
     <row r="5154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5154" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5154" s="7">
         <v>8.5</v>
@@ -59353,7 +59350,7 @@
     </row>
     <row r="5155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5155" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5155" s="7">
         <v>15.5</v>
@@ -59364,7 +59361,7 @@
     </row>
     <row r="5156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5156" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5156" s="7">
         <v>8</v>
@@ -59375,7 +59372,7 @@
     </row>
     <row r="5157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5157" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5157" s="7">
         <v>31</v>
@@ -59386,7 +59383,7 @@
     </row>
     <row r="5158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5158" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5158" s="7">
         <v>6.5</v>
@@ -59397,7 +59394,7 @@
     </row>
     <row r="5159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5159" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5159" s="7">
         <v>9</v>
@@ -59408,7 +59405,7 @@
     </row>
     <row r="5160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5160" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5160" s="7">
         <v>5</v>
@@ -59419,7 +59416,7 @@
     </row>
     <row r="5161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5161" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5161" s="7">
         <v>2.5</v>
@@ -59430,7 +59427,7 @@
     </row>
     <row r="5162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5162" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5162" s="7">
         <v>12</v>
@@ -59441,7 +59438,7 @@
     </row>
     <row r="5163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5163" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5163" s="7">
         <v>7</v>
@@ -59452,7 +59449,7 @@
     </row>
     <row r="5164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5164" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5164" s="7">
         <v>15</v>
@@ -59463,7 +59460,7 @@
     </row>
     <row r="5165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5165" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5165" s="7">
         <v>14.5</v>
@@ -59474,7 +59471,7 @@
     </row>
     <row r="5166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5166" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B5166" s="7">
         <v>20</v>
@@ -59485,7 +59482,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C5166">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
